--- a/logs/encoders/random_seed_runs.xlsx
+++ b/logs/encoders/random_seed_runs.xlsx
@@ -1,29 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ddore/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ddore/Documents/RooseBERT/logs/encoders/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67642286-C526-A843-B12A-86D0CCB07CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA54491-0A8D-5B45-9B71-2FD2E6D2415E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19400" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="argument_detection" sheetId="1" r:id="rId1"/>
-    <sheet name="ner" sheetId="2" r:id="rId2"/>
-    <sheet name="relation_classification" sheetId="3" r:id="rId3"/>
-    <sheet name="sentiment_analysis" sheetId="4" r:id="rId4"/>
+    <sheet name="relation_classification" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="67">
   <si>
     <t>Models</t>
   </si>
@@ -163,69 +161,6 @@
     <t>[0.4754929123599369, 0.4762467521914967, 0.4735636878779057, 0.4725968995000967, 0.4767252816503108]</t>
   </si>
   <si>
-    <t>[0.5025999242631661, 0.5047502009751268, 0.5013404922520726, 0.5001024617932216, 0.4860517076953067]</t>
-  </si>
-  <si>
-    <t>[0.5052085716063764, 0.4827218240034983, 0.4930639070335546, 0.4901258593207117, 0.4885732774574944]</t>
-  </si>
-  <si>
-    <t>[0.3471730220275356, 0.3075304746015462, 0.2905573289842906, 0.3596336107341115, 0.3875956782960063]</t>
-  </si>
-  <si>
-    <t>[0.4529441496619166, 0.4352611694127309, 0.446772333411863, 0.4513281651860034, 0.4193036404339764]</t>
-  </si>
-  <si>
-    <t>[0.4165955303550888, 0.265407101597311, 0.4365664637623362, 0.437078040362541, 0.3913871176105853]</t>
-  </si>
-  <si>
-    <t>[0.5684053687647564, 0.5219882189310036, 0.2235039523464101, 0.5514172753531305, 0.5934409163310104]</t>
-  </si>
-  <si>
-    <t>[0.5269760589418356, 0.5396195768231203, 0.5153452728682443, 0.5348391924003211, 0.5235415008080723]</t>
-  </si>
-  <si>
-    <t>[0.5396444979686671, 0.5417190143112405, 0.0387767804809303, 0.4990128807387654, 0.4751615359808779]</t>
-  </si>
-  <si>
-    <t>[0.484553046091569, 0.4551666036726114, 0.478194873692705, 0.5055377271263205, 0.4598516271192195]</t>
-  </si>
-  <si>
-    <t>[0.5204757400493576, 0.5154708671581938, 0.5136952017223149, 0.5148983531811705, 0.52408003280462]</t>
-  </si>
-  <si>
-    <t>[0.4982200440114481, 0.4837676596690606, 0.4977693697750333, 0.4732222033378968, 0.4683385376794824]</t>
-  </si>
-  <si>
-    <t>[0.4948601956341019, 0.511912425134853, 0.5141746054203994, 0.4965183026600258, 0.5002469090316136]</t>
-  </si>
-  <si>
-    <t>[0.5738007849947497, 0.580496476738692, 0.5725407091692375, 0.5769415726269214, 0.553834097113182]</t>
-  </si>
-  <si>
-    <t>[0.6080306833513516, 0.6114867304980549, 0.5673508511814433, 0.6072225337162088, 0.5739466959363724]</t>
-  </si>
-  <si>
-    <t>[0.5101717490891027, 0.5376582647417688, 0.5017675614238707, 0.5051419021478635, 0.523902605440326]</t>
-  </si>
-  <si>
-    <t>[0.50596606628106, 0.4834189916897693, 0.4938528519714759, 0.4989885384685556, 0.4766021417526367]</t>
-  </si>
-  <si>
-    <t>[0.5021825588338464, 0.4817918709268132, 0.5078022584799153, 0.4941518563165316, 0.4710669659130245]</t>
-  </si>
-  <si>
-    <t>[0.487145123033121, 0.4772555177365324, 0.4942528377433034, 0.4774283089446736, 0.4834681557954507]</t>
-  </si>
-  <si>
-    <t>[0.5335199890152458, 0.5254870115998177, 0.5263881871169188, 0.5192990215505597, 0.5100922066538988]</t>
-  </si>
-  <si>
-    <t>[0.4787372902117905, 0.4713900626851962, 0.4646137613262087, 0.4669909615740761, 0.4411527975230292]</t>
-  </si>
-  <si>
-    <t>[0.5528220904974287, 0.5605946740563337, 0.5554715454938561, 0.5489262136330056, 0.5453035105341261]</t>
-  </si>
-  <si>
     <t>[0.6849165662575398, 0.6613807386582377, 0.6579401480746561, 0.6739493140058292, 0.66535167368993]</t>
   </si>
   <si>
@@ -287,66 +222,6 @@
   </si>
   <si>
     <t>[0.6973165685711692, 0.1986791414419372, 0.6865454090083626, 0.2222802891734169, 0.691232665275483]</t>
-  </si>
-  <si>
-    <t>[0.7198917456021651, 0.7363445378151261, 0.7267217630853995, 0.7206673842841765, 0.7192446542627048]</t>
-  </si>
-  <si>
-    <t>[0.7293354943273906, 0.7265856950067476, 0.7181767648693719, 0.7248285322359397, 0.7262357414448669]</t>
-  </si>
-  <si>
-    <t>[0.6911793467631527, 0.6555133079847909, 0.6284953395472703, 0.6555386949924128, 0.6385350318471338]</t>
-  </si>
-  <si>
-    <t>[0.6911793467631527, 0.6964907581034021, 0.679606342263532, 0.6685267857142857, 0.6768325307651151]</t>
-  </si>
-  <si>
-    <t>[0.7180336923501796, 0.7231484012025143, 0.7260689655172414, 0.7300297860817764, 0.7309700467161308]</t>
-  </si>
-  <si>
-    <t>[0.6911793467631527, 0.6911793467631527, 0.6911793467631527, 0.6361095584125209, 0.6911793467631527]</t>
-  </si>
-  <si>
-    <t>[0.6911793467631527, 0.5943396226415094, 0.6755106338176459, 0.6911793467631527, 0.6245278267438932]</t>
-  </si>
-  <si>
-    <t>[0.7232243517474634, 0.6911793467631527, 0.7208580299181485, 0.719170403587444, 0.7192063929457151]</t>
-  </si>
-  <si>
-    <t>[0.7352463454250135, 0.7217920353982301, 0.7157318741450068, 0.7346269472533479, 0.7207598371777476]</t>
-  </si>
-  <si>
-    <t>[0.6768081131571925, 0.6644968809330078, 0.6611111111111111, 0.6816192560175055, 0.6911793467631527]</t>
-  </si>
-  <si>
-    <t>[0.7340339531123686, 0.7236016371077763, 0.7341981783052719, 0.7320547945205479, 0.7358541163850898]</t>
-  </si>
-  <si>
-    <t>[0.6911793467631527, 0.6911793467631527, 0.6911793467631527, 0.6911793467631527, 0.6836228287841191]</t>
-  </si>
-  <si>
-    <t>[0.714008321775312, 0.7239794539064612, 0.7160146355192795, 0.7141668976989187, 0.7147540983606557]</t>
-  </si>
-  <si>
-    <t>[0.6911793467631527, 0.6911793467631527, 0.6911793467631527, 0.6911793467631527, 0.6911793467631527]</t>
-  </si>
-  <si>
-    <t>[0.6839609483960949, 0.6939799331103679, 0.6964873765093305, 0.6909294512877939, 0.6983346983346983]</t>
-  </si>
-  <si>
-    <t>[0.7354309165526676, 0.7427792915531335, 0.7204691426975706, 0.7299670691547749, 0.7388120423108218]</t>
-  </si>
-  <si>
-    <t>[0.7323561346362649, 0.73021090112298, 0.7300167691447736, 0.7226615762203437, 0.725]</t>
-  </si>
-  <si>
-    <t>[0.718186783178591, 0.7155865024102839, 0.7227993439037725, 0.7167851284855112, 0.7142064372918979]</t>
-  </si>
-  <si>
-    <t>[0.7337212524244944, 0.7317880794701986, 0.7364975450081833, 0.7353022357162572, 0.7320940404592674]</t>
-  </si>
-  <si>
-    <t>[0.7150837988826816, 0.7213114754098361, 0.7067583046964491, 0.7241664370349958, 0.7247956403269755]</t>
   </si>
 </sst>
 </file>
@@ -1048,333 +923,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="42.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="112.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.83203125" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="1">
-        <v>0.52800000000000002</v>
-      </c>
-      <c r="C2" s="1">
-        <v>0.01</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="1">
-        <v>0.504</v>
-      </c>
-      <c r="C3" s="1">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="1">
-        <v>0.59399999999999997</v>
-      </c>
-      <c r="C4" s="1">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1">
-        <v>0.49199999999999999</v>
-      </c>
-      <c r="C5" s="1">
-        <v>0.152</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1">
-        <v>0.441</v>
-      </c>
-      <c r="C6" s="1">
-        <v>1.4E-2</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="1">
-        <v>0.49199999999999999</v>
-      </c>
-      <c r="C7" s="1">
-        <v>1.2E-2</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="1">
-        <v>0.51800000000000002</v>
-      </c>
-      <c r="C8" s="1">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="1">
-        <v>0.51600000000000001</v>
-      </c>
-      <c r="C9" s="1">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1">
-        <v>0.33800000000000002</v>
-      </c>
-      <c r="C10" s="1">
-        <v>3.9E-2</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="1">
-        <v>0.47699999999999998</v>
-      </c>
-      <c r="C11" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="1">
-        <v>0.38900000000000001</v>
-      </c>
-      <c r="C12" s="1">
-        <v>7.1999999999999995E-2</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" s="1">
-        <v>0.55300000000000005</v>
-      </c>
-      <c r="C13" s="1">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="1">
-        <v>0.41899999999999998</v>
-      </c>
-      <c r="C14" s="1">
-        <v>0.214</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="1">
-        <v>0.57199999999999995</v>
-      </c>
-      <c r="C15" s="1">
-        <v>0.01</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="1">
-        <v>0.52300000000000002</v>
-      </c>
-      <c r="C16" s="1">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="1">
-        <v>0.499</v>
-      </c>
-      <c r="C17" s="1">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="1">
-        <v>0.48399999999999999</v>
-      </c>
-      <c r="C18" s="1">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="1">
-        <v>0.49099999999999999</v>
-      </c>
-      <c r="C19" s="1">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="1">
-        <v>0.48399999999999999</v>
-      </c>
-      <c r="C20" s="1">
-        <v>1.4E-2</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="1">
-        <v>0.49199999999999999</v>
-      </c>
-      <c r="C21" s="1">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="1">
-        <v>0.46500000000000002</v>
-      </c>
-      <c r="C22" s="1">
-        <v>1.4E-2</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D23">
-    <sortCondition ref="A1:A23"/>
-  </sortState>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
@@ -1410,7 +958,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1424,7 +972,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1438,7 +986,7 @@
         <v>0.19800000000000001</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1452,7 +1000,7 @@
         <v>0.28299999999999997</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1466,7 +1014,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1480,7 +1028,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1494,7 +1042,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1508,7 +1056,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1522,7 +1070,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1536,7 +1084,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1550,7 +1098,7 @@
         <v>0.109</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1564,7 +1112,7 @@
         <v>0.26400000000000001</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1578,7 +1126,7 @@
         <v>0.21</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1592,7 +1140,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1606,7 +1154,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1620,7 +1168,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1634,7 +1182,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1648,7 +1196,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1662,7 +1210,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1676,7 +1224,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1690,7 +1238,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1699,331 +1247,4 @@
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="42.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="112.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.83203125" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="1">
-        <v>0.65500000000000003</v>
-      </c>
-      <c r="C2" s="1">
-        <v>4.3999999999999997E-2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="1">
-        <v>0.69</v>
-      </c>
-      <c r="C3" s="1">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="1">
-        <v>0.69099999999999995</v>
-      </c>
-      <c r="C4" s="1">
-        <v>0</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="C5" s="1">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1">
-        <v>0.68300000000000005</v>
-      </c>
-      <c r="C6" s="1">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="1">
-        <v>0.69099999999999995</v>
-      </c>
-      <c r="C7" s="1">
-        <v>0</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="1">
-        <v>0.67500000000000004</v>
-      </c>
-      <c r="C8" s="1">
-        <v>1.2E-2</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="1">
-        <v>0.69299999999999995</v>
-      </c>
-      <c r="C9" s="1">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1">
-        <v>0.65400000000000003</v>
-      </c>
-      <c r="C10" s="1">
-        <v>2.4E-2</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="1">
-        <v>0.72599999999999998</v>
-      </c>
-      <c r="C11" s="1">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="1">
-        <v>0.72599999999999998</v>
-      </c>
-      <c r="C12" s="1">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" s="1">
-        <v>0.71799999999999997</v>
-      </c>
-      <c r="C13" s="1">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="1">
-        <v>0.71499999999999997</v>
-      </c>
-      <c r="C14" s="1">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="1">
-        <v>0.71699999999999997</v>
-      </c>
-      <c r="C15" s="1">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="1">
-        <v>0.71799999999999997</v>
-      </c>
-      <c r="C16" s="1">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="1">
-        <v>0.72499999999999998</v>
-      </c>
-      <c r="C17" s="1">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="1">
-        <v>0.72799999999999998</v>
-      </c>
-      <c r="C18" s="1">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="1">
-        <v>0.73299999999999998</v>
-      </c>
-      <c r="C19" s="1">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="1">
-        <v>0.73199999999999998</v>
-      </c>
-      <c r="C20" s="1">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="1">
-        <v>0.72499999999999998</v>
-      </c>
-      <c r="C21" s="1">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="1">
-        <v>0.73399999999999999</v>
-      </c>
-      <c r="C22" s="1">
-        <v>2E-3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D23">
-    <sortCondition ref="A1:A23"/>
-  </sortState>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/logs/encoders/random_seed_runs.xlsx
+++ b/logs/encoders/random_seed_runs.xlsx
@@ -8,20 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ddore/Documents/RooseBERT/logs/encoders/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA54491-0A8D-5B45-9B71-2FD2E6D2415E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{201FFA78-EBB1-0740-9F8F-5946BA586891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="argument_detection" sheetId="1" r:id="rId1"/>
     <sheet name="relation_classification" sheetId="3" r:id="rId2"/>
+    <sheet name="sentiment_analysis" sheetId="4" r:id="rId3"/>
+    <sheet name="stance_detection " sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="78">
   <si>
     <t>Models</t>
   </si>
@@ -222,6 +224,39 @@
   </si>
   <si>
     <t>[0.6973165685711692, 0.1986791414419372, 0.6865454090083626, 0.2222802891734169, 0.691232665275483]</t>
+  </si>
+  <si>
+    <t>[0.4334713143113939, 0.4217632103442539, 0.4297976185521515, 0.4316164651749934, 0.4034338627939364]</t>
+  </si>
+  <si>
+    <t>[0.4214632575996459, 0.412292024143628, 0.4084637940463122, 0.4119063531487308, 0.4160189114379384]</t>
+  </si>
+  <si>
+    <t>[0.4150979296964867, 0.4174981997306166, 0.4004981617872298, 0.4246847373128025, 0.4165492363355412]</t>
+  </si>
+  <si>
+    <t>[0.4274168509507991, 0.4080486256291798, 0.4158043414209346, 0.4001091654664204, 0.4035700807677971]</t>
+  </si>
+  <si>
+    <t>[0.4257784017536474, 0.4297646752056605, 0.4251034800489351, 0.4070913214068026, 0.4205923431216856]</t>
+  </si>
+  <si>
+    <t>[0.423960711404246, 0.4257053619336227, 0.4320494988594704, 0.4056098930404643, 0.4071933278469172]</t>
+  </si>
+  <si>
+    <t>[0.4078257305578256, 0.4125000292973657, 0.4098652342703324, 0.4052120568088863, 0.4066176929542449]</t>
+  </si>
+  <si>
+    <t>[0.4437083051025244, 0.4214002111604292, 0.4010793170137043, 0.4344208726107019, 0.4251273627726575]</t>
+  </si>
+  <si>
+    <t>[0.4280969814772259, 0.4214571260163464, 0.4157919185684081, 0.422931923925346, 0.4083553182019861]</t>
+  </si>
+  <si>
+    <t>[0.4372961690889643, 0.445915616943118, 0.4254334069934886, 0.4373053789636054, 0.2873582743511965]</t>
+  </si>
+  <si>
+    <t>[0.4094528871344726, 0.4052810228839861, 0.4083697081984964, 0.3604162443528734, 0.4094040712524975]</t>
   </si>
 </sst>
 </file>
@@ -1247,4 +1282,200 @@
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7333CB4-095B-5D43-BC7B-7890FCCD3CA2}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08CAF02F-8228-BE47-96D8-6960E765A3B1}">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="42.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="112.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1.6E-2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.42399999999999999</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1.2E-2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.42199999999999999</v>
+      </c>
+      <c r="C4" s="1">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.41899999999999998</v>
+      </c>
+      <c r="C5" s="1">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.41899999999999998</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1.2E-2</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0.41499999999999998</v>
+      </c>
+      <c r="C7" s="1">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0.41399999999999998</v>
+      </c>
+      <c r="C8" s="1">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0.41099999999999998</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0.40799999999999997</v>
+      </c>
+      <c r="C10" s="1">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1">
+        <v>0.40699999999999997</v>
+      </c>
+      <c r="C11" s="1">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="1">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D12">
+    <sortCondition descending="1" ref="B1:B12"/>
+  </sortState>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/logs/encoders/random_seed_runs.xlsx
+++ b/logs/encoders/random_seed_runs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ddore/Documents/RooseBERT/logs/encoders/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{201FFA78-EBB1-0740-9F8F-5946BA586891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6706480A-B90D-8A4D-9852-CB9127560571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="89">
   <si>
     <t>Models</t>
   </si>
@@ -257,13 +257,46 @@
   </si>
   <si>
     <t>[0.4094528871344726, 0.4052810228839861, 0.4083697081984964, 0.3604162443528734, 0.4094040712524975]</t>
+  </si>
+  <si>
+    <t>[0.6123729826658697, 0.6132695756126718, 0.6180514046622834, 0.6270173341303048, 0.6270173341303048]</t>
+  </si>
+  <si>
+    <t>[0.6288105200239091, 0.6108786610878661, 0.6195457262402869, 0.6291093843395099, 0.625821876867902]</t>
+  </si>
+  <si>
+    <t>[0.6524208009563658, 0.6569037656903766, 0.6569037656903766, 0.6607890017931859, 0.661685594739988]</t>
+  </si>
+  <si>
+    <t>[0.6410639569635386, 0.6464435146443515, 0.6536162582187687, 0.6449491930663479, 0.6365809922295278]</t>
+  </si>
+  <si>
+    <t>[0.6306037059175135, 0.6326957561267185, 0.6545128511655708, 0.6494321578003587, 0.6539151225343693]</t>
+  </si>
+  <si>
+    <t>[0.5463239689181112, 0.6640765092647938, 0.6297071129707112, 0.6607890017931859, 0.661685594739988]</t>
+  </si>
+  <si>
+    <t>[0.5953377166766288, 0.5944411237298266, 0.5780035863717872, 0.6144650328750747, 0.5959354453078303]</t>
+  </si>
+  <si>
+    <t>[0.6918708906156605, 0.6826060968320382, 0.6984459055588763, 0.6903765690376569, 0.7002390914524805]</t>
+  </si>
+  <si>
+    <t>[0.7020322773460849, 0.6885833831440527, 0.7014345487148834, 0.6963538553496712, 0.7065152420800956]</t>
+  </si>
+  <si>
+    <t>[0.6984459055588763, 0.7023311416616856, 0.696652719665272, 0.6918708906156605, 0.6921697549312612]</t>
+  </si>
+  <si>
+    <t>[0.7002390914524805, 0.7020322773460849, 0.7083084279737, 0.6972504482964734, 0.7017334130304842]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -280,6 +313,13 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri (Corpo)"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -323,13 +363,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1286,9 +1327,184 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7333CB4-095B-5D43-BC7B-7890FCCD3CA2}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="42.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="7" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="112.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.83203125" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="C2" s="1">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.623</v>
+      </c>
+      <c r="C3" s="1">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.65800000000000003</v>
+      </c>
+      <c r="C4" s="1">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.64500000000000002</v>
+      </c>
+      <c r="C5" s="1">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.64400000000000002</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1.2E-2</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0.63300000000000001</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0.59599999999999997</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0.69299999999999995</v>
+      </c>
+      <c r="C9" s="1">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0.69899999999999995</v>
+      </c>
+      <c r="C10" s="1">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="1">
+        <v>0.69599999999999995</v>
+      </c>
+      <c r="C11" s="1">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="1">
+        <v>0.70199999999999996</v>
+      </c>
+      <c r="C12" s="1">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/logs/encoders/random_seed_runs.xlsx
+++ b/logs/encoders/random_seed_runs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ddore/Documents/RooseBERT/logs/encoders/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6706480A-B90D-8A4D-9852-CB9127560571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A7833CE-F79C-4E4F-86D8-AD8AB36FC4C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5860" yWindow="3220" windowWidth="28800" windowHeight="15800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="argument_detection" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="95">
   <si>
     <t>Models</t>
   </si>
@@ -290,6 +290,24 @@
   </si>
   <si>
     <t>[0.7002390914524805, 0.7020322773460849, 0.7083084279737, 0.6972504482964734, 0.7017334130304842]</t>
+  </si>
+  <si>
+    <t>[0.7133891213389121, 0.7023311416616856, 0.7080095636580992, 0.7056186491332935, 0.7172743574417214]</t>
+  </si>
+  <si>
+    <t>[0.7098027495517035, 0.7253436939629408, 0.7244471010161386, 0.7151823072325164, 0.7205618649133293]</t>
+  </si>
+  <si>
+    <t>[0.7304243873281531, 0.735803945008966, 0.7226539151225344, 0.7274357441721458, 0.5280932456664674]</t>
+  </si>
+  <si>
+    <t>[0.7229527794381351, 0.7136879856545129, 0.7148834429169157, 0.7139868499701135, 0.7092050209205021]</t>
+  </si>
+  <si>
+    <t>[0.6078900179318589, 0.5280932456664674, 0.5280932456664674, 0.5280932456664674, 0.5280932456664674]</t>
+  </si>
+  <si>
+    <t>[0.5280932456664674, 0.5280932456664674, 0.5280932456664674, 0.5280932456664674, 0.5280932456664674]</t>
   </si>
 </sst>
 </file>
@@ -1327,7 +1345,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7333CB4-095B-5D43-BC7B-7890FCCD3CA2}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.33203125" style="4" bestFit="1" customWidth="1"/>
@@ -1502,6 +1520,90 @@
       </c>
       <c r="D12" s="1" t="s">
         <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="1">
+        <v>0.70899999999999996</v>
+      </c>
+      <c r="C13" s="1">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="1">
+        <v>0.71899999999999997</v>
+      </c>
+      <c r="C14" s="1">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="1">
+        <v>0.68899999999999995</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="1">
+        <v>0.71499999999999997</v>
+      </c>
+      <c r="C16" s="1">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1">
+        <v>0.54400000000000004</v>
+      </c>
+      <c r="C17" s="1">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="1">
+        <v>0.52800000000000002</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/logs/encoders/random_seed_runs.xlsx
+++ b/logs/encoders/random_seed_runs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ddore/Documents/RooseBERT/logs/encoders/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A7833CE-F79C-4E4F-86D8-AD8AB36FC4C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38461C5E-96C2-7C46-B749-EA0426B000B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5860" yWindow="3220" windowWidth="28800" windowHeight="15800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5860" yWindow="3220" windowWidth="28800" windowHeight="15800" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="argument_detection" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="101">
   <si>
     <t>Models</t>
   </si>
@@ -308,6 +308,24 @@
   </si>
   <si>
     <t>[0.5280932456664674, 0.5280932456664674, 0.5280932456664674, 0.5280932456664674, 0.5280932456664674]</t>
+  </si>
+  <si>
+    <t>[0.4155015300756659, 0.4329528272394403, 0.4031166372718638, 0.4196605348526328, 0.4261661999134556]</t>
+  </si>
+  <si>
+    <t>[0.4245976378218252, 0.1605322274062554, 0.4235551211679018, 0.4339131740182059, 0.3931337174428217]</t>
+  </si>
+  <si>
+    <t>[0.4056238076527814, 0.3914071015332916, 0.1605322274062554, 0.1605322274062554, 0.3839662413248567]</t>
+  </si>
+  <si>
+    <t>[0.4208751624110127, 0.4130150856852466, 0.4064710002122024, 0.4190001231713768, 0.4027294294507512]</t>
+  </si>
+  <si>
+    <t>[0.3416141209052408, 0.3420588400472473, 0.3461646263125992, 0.4070393200999325, 0.3226089470269201]</t>
+  </si>
+  <si>
+    <t>[0.1690451919809718, 0.2733330311862034, 0.4030573455239607, 0.3572911321719844, 0.377583780827645]</t>
   </si>
 </sst>
 </file>
@@ -1613,7 +1631,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08CAF02F-8228-BE47-96D8-6960E765A3B1}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -1790,6 +1808,90 @@
         <v>77</v>
       </c>
     </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="4">
+        <v>0.41899999999999998</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="4">
+        <v>0.36699999999999999</v>
+      </c>
+      <c r="C14" s="4">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="C15" s="4">
+        <v>0.128</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="4">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="C16" s="4">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="4">
+        <v>0.35199999999999998</v>
+      </c>
+      <c r="C17" s="4">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="4">
+        <v>0.316</v>
+      </c>
+      <c r="C18" s="4">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D12">
     <sortCondition descending="1" ref="B1:B12"/>
